--- a/Hardware/Mini-Decoder/Jukebox-small-PCB-BOM.xlsx
+++ b/Hardware/Mini-Decoder/Jukebox-small-PCB-BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lafleur/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4537B39-86BA-E84B-A246-089BDEC7E2D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{21A4AD50-6F3B-E446-8E22-0D37C75865E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="21500" yWindow="10980" windowWidth="18300" windowHeight="17760" xr2:uid="{AB5A083E-1DFE-2640-8C11-1501A1C90952}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="70">
   <si>
     <t>Description</t>
   </si>
@@ -240,6 +240,12 @@
   </si>
   <si>
     <t>Please note, I used parts from my inventory to build this, parts substitute may be needed...</t>
+  </si>
+  <si>
+    <t>TDK</t>
+  </si>
+  <si>
+    <t>B41888C6477M</t>
   </si>
 </sst>
 </file>
@@ -672,7 +678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAFA94AD-1E7D-D745-98D5-5BE63D13CE37}">
-  <dimension ref="A3:G33"/>
+  <dimension ref="A3:G34"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="31.83203125" customWidth="1"/>
@@ -804,36 +810,33 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
+      <c r="F14" t="s">
+        <v>68</v>
+      </c>
+      <c r="G14" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B15" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>48</v>
-      </c>
-      <c r="D17" s="4" t="s">
+      <c r="D15" s="4" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>24</v>
@@ -841,132 +844,143 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>18</v>
-      </c>
-      <c r="B22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G22" t="s">
-        <v>37</v>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" t="s">
+        <v>38</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="G23" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
         <v>19</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B24" t="s">
         <v>40</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D24" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F24" t="s">
         <v>41</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G24" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="G24" t="s">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="G25" t="s">
         <v>57</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>20</v>
-      </c>
-      <c r="B25" t="s">
-        <v>57</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F25" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B26" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="F26" t="s">
-        <v>60</v>
-      </c>
-      <c r="G26" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
+        <v>21</v>
+      </c>
+      <c r="B27" t="s">
+        <v>43</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F27" t="s">
+        <v>60</v>
+      </c>
+      <c r="G27" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
         <v>52</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B28" t="s">
         <v>53</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="D28" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F28" t="s">
         <v>54</v>
       </c>
-      <c r="G27" t="s">
+      <c r="G28" t="s">
         <v>56</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>22</v>
-      </c>
-      <c r="B29" t="s">
-        <v>45</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30" t="s">
+        <v>45</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
         <v>23</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B31" t="s">
         <v>46</v>
       </c>
-      <c r="D30" s="7" t="s">
+      <c r="D31" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="F30" t="s">
+      <c r="F31" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.2">
-      <c r="B33" t="s">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B34" t="s">
         <v>67</v>
       </c>
     </row>
@@ -974,7 +988,7 @@
   <hyperlinks>
     <hyperlink ref="F7" r:id="rId1" display="https://www.mouser.com/en/manufacturer/diodes-inc/" xr:uid="{6AE10B98-1085-9D42-8E39-D53B89282291}"/>
     <hyperlink ref="F8" r:id="rId2" display="https://www.mouser.com/en/manufacturer/diodes-inc/" xr:uid="{DDD89A5A-521E-194B-B6E8-4BBCDE88DBD4}"/>
-    <hyperlink ref="F22" r:id="rId3" display="https://www.digikey.com/en/supplier-centers/lite-on" xr:uid="{51B97279-5C8F-024F-8AC6-2F8C5EA82EF2}"/>
+    <hyperlink ref="F23" r:id="rId3" display="https://www.digikey.com/en/supplier-centers/lite-on" xr:uid="{51B97279-5C8F-024F-8AC6-2F8C5EA82EF2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Hardware/Mini-Decoder/Jukebox-small-PCB-BOM.xlsx
+++ b/Hardware/Mini-Decoder/Jukebox-small-PCB-BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lafleur/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{21A4AD50-6F3B-E446-8E22-0D37C75865E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F84991D-C049-9D40-8D16-82249E017231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="21500" yWindow="10980" windowWidth="18300" windowHeight="17760" xr2:uid="{AB5A083E-1DFE-2640-8C11-1501A1C90952}"/>
   </bookViews>
@@ -170,9 +170,6 @@
     <t>ESP32-S3</t>
   </si>
   <si>
-    <t>14pin DIP</t>
-  </si>
-  <si>
     <t>Led Red</t>
   </si>
   <si>
@@ -246,6 +243,9 @@
   </si>
   <si>
     <t>B41888C6477M</t>
+  </si>
+  <si>
+    <t>14pin SIP</t>
   </si>
 </sst>
 </file>
@@ -727,10 +727,10 @@
         <v>30</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>28</v>
@@ -747,10 +747,10 @@
         <v>30</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>28</v>
@@ -803,18 +803,18 @@
         <v>33</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" t="s">
         <v>65</v>
-      </c>
-      <c r="F13" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="F14" t="s">
+        <v>67</v>
+      </c>
+      <c r="G14" t="s">
         <v>68</v>
-      </c>
-      <c r="G14" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
@@ -825,7 +825,7 @@
         <v>34</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>24</v>
@@ -836,7 +836,7 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>24</v>
@@ -847,7 +847,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>24</v>
@@ -858,7 +858,7 @@
         <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>24</v>
@@ -900,7 +900,7 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="G25" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
@@ -908,13 +908,13 @@
         <v>20</v>
       </c>
       <c r="B26" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F26" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
@@ -925,33 +925,33 @@
         <v>43</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>44</v>
+        <v>69</v>
       </c>
       <c r="F27" t="s">
+        <v>59</v>
+      </c>
+      <c r="G27" t="s">
         <v>60</v>
-      </c>
-      <c r="G27" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
+        <v>51</v>
+      </c>
+      <c r="B28" t="s">
         <v>52</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="F28" t="s">
         <v>53</v>
       </c>
-      <c r="C28" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D28" s="7" t="s">
+      <c r="G28" t="s">
         <v>55</v>
-      </c>
-      <c r="F28" t="s">
-        <v>54</v>
-      </c>
-      <c r="G28" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
@@ -959,7 +959,7 @@
         <v>22</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>24</v>
@@ -970,18 +970,18 @@
         <v>23</v>
       </c>
       <c r="B31" t="s">
+        <v>45</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="F31" t="s">
         <v>46</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="F31" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B34" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
